--- a/Excel/03.sample-data-mod by omkar.blank.xlsx
+++ b/Excel/03.sample-data-mod by omkar.blank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D3272E-1672-4CFE-88DA-B03FACF09773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0899542-B966-4859-A257-2946943A72FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="10" xr2:uid="{26D4546B-D2A1-4444-8EAF-A6228F96F0C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Concepts" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <sheet name="FILTER,star" sheetId="4" r:id="rId4"/>
     <sheet name="MIN,MAX,LARGE,SORT,TAKE" sheetId="5" r:id="rId5"/>
     <sheet name="UNIQUE,COUNTA,HASH" sheetId="6" r:id="rId6"/>
+    <sheet name="VLOOKUP,INDEX,MATCH" sheetId="7" r:id="rId7"/>
+    <sheet name="XLOOKUP,IFERROR" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet3" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet4" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2512" uniqueCount="858">
   <si>
     <t>Emp ID</t>
   </si>
@@ -2433,18 +2438,457 @@
   </si>
   <si>
     <t>All departments in one cell Comma seperated</t>
+  </si>
+  <si>
+    <t>Employee Lookup</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>First name:</t>
+  </si>
+  <si>
+    <t>Last name:</t>
+  </si>
+  <si>
+    <t>Salary:</t>
+  </si>
+  <si>
+    <t>PR0387</t>
+  </si>
+  <si>
+    <t>Employee id:</t>
+  </si>
+  <si>
+    <t>Index of row:</t>
+  </si>
+  <si>
+    <t>With XLOOKUP</t>
+  </si>
+  <si>
+    <t>Entire Data</t>
+  </si>
+  <si>
+    <t>Complex Formula :Highest Salary Person</t>
+  </si>
+  <si>
+    <t>All Persons:</t>
+  </si>
+  <si>
+    <t>Highest Salary:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Person with highest salary:</t>
+  </si>
+  <si>
+    <t>First Name + Last Name :</t>
+  </si>
+  <si>
+    <t>Comma seperated:</t>
+  </si>
+  <si>
+    <t>XLOOKUP + MAX + FILTER – Explanation</t>
+  </si>
+  <si>
+    <t>These are four useful formulas for finding employees with the highest salary.</t>
+  </si>
+  <si>
+    <t>1. Find the first name of the highest-paid employee</t>
+  </si>
+  <si>
+    <r>
+      <t>MAX()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> finds the highest salary.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>XLOOKUP()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> searches for that salary.</t>
+    </r>
+  </si>
+  <si>
+    <t>Returns the first matching employee's first name.</t>
+  </si>
+  <si>
+    <t>2. Find the full name of the highest-paid employee</t>
+  </si>
+  <si>
+    <t>Combines First Name and Last Name and returns the full name.</t>
+  </si>
+  <si>
+    <t>Note: If multiple employees have the same highest salary, XLOOKUP returns only the first match.</t>
+  </si>
+  <si>
+    <t>3. Find all employees with the highest salary</t>
+  </si>
+  <si>
+    <r>
+      <t>FILTER()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns all employees whose salary equals that maximum.</t>
+    </r>
+  </si>
+  <si>
+    <t>Handles multiple employees with the same highest salary.</t>
+  </si>
+  <si>
+    <t>4. Display all their names in one cell</t>
+  </si>
+  <si>
+    <t>Combines all matching first names into one cell, separated by commas.</t>
+  </si>
+  <si>
+    <t>Quick comparison</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>First matching employee</t>
+  </si>
+  <si>
+    <t>XLOOKUP + MAX + concatenation</t>
+  </si>
+  <si>
+    <t>First matching full name</t>
+  </si>
+  <si>
+    <t>FILTER + MAX</t>
+  </si>
+  <si>
+    <t>All matching employees</t>
+  </si>
+  <si>
+    <t>TEXTJOIN + FILTER + MAX</t>
+  </si>
+  <si>
+    <t>All matching names in one cell</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Important takeaway: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>XLOOKUP()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns the first match; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>FILTER()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns all matches.</t>
+    </r>
+  </si>
+  <si>
+    <t>People whose name starts with letter H</t>
+  </si>
+  <si>
+    <t>All Employees who joined in march</t>
+  </si>
+  <si>
+    <t>All female employees that have started on Monday</t>
+  </si>
+  <si>
+    <t>1. Filter names starting with H</t>
+  </si>
+  <si>
+    <r>
+      <t>LEFT(text, num_chars)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extracts characters from the left.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LEFT(staff[First Name],1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> extracts the first character of each employee's first name.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>="H"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> checks whether that character is H.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FILTER()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns the full rows for matching employees.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MONTH(date)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns the month number from a date (January = 1, March = 3, etc.).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MONTH(staff[Start Date])=3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> checks whether each employee joined in March.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>staff[[Emp ID]:[Last Name]]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns only the Emp ID and Last Name columns.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FILTER()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns those columns for matching employees.</t>
+    </r>
+  </si>
+  <si>
+    <t>Note: This includes March dates from every year.</t>
+  </si>
+  <si>
+    <t>Filter employees who joined in March</t>
+  </si>
+  <si>
+    <t>Female employees who joined on Monday</t>
+  </si>
+  <si>
+    <r>
+      <t>WEEKDAY(date,2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns Monday = 1 through Sunday = 7.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WEEKDAY(...)=1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> checks whether the start date was a Monday.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>staff[Gender]="Female"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> checks whether the employee is female.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> combines the conditions using AND logic: both must be true.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FILTER()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> returns the full rows for employees matching both conditions.</t>
+    </r>
+  </si>
+  <si>
+    <t>All Departments</t>
+  </si>
+  <si>
+    <t>headcount</t>
+  </si>
+  <si>
+    <t>Avg salary</t>
+  </si>
+  <si>
+    <t>Highest salary</t>
+  </si>
+  <si>
+    <t>% diff from  avg salary</t>
+  </si>
+  <si>
+    <t>Median Salary</t>
+  </si>
+  <si>
+    <t>Female Ratio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="173" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="175" formatCode="[$$-409]#,##0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2510,8 +2954,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2572,6 +3046,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2620,11 +3106,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2707,10 +3194,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="2" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -2850,13 +3378,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}" name="staff" displayName="staff" ref="C7:O267" totalsRowShown="0">
-  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="greaterThanOrEqual" val="100000"/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="C7:O267" xr:uid="{71B18D4F-F180-46A4-9272-AD02F8205A18}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{943DE765-0286-4102-BD68-49CEED7DAF5A}" name="Emp ID"/>
     <tableColumn id="2" xr3:uid="{45228A4A-AEEB-4CEE-80B5-33BA9570C47D}" name="First Name"/>
@@ -4639,6 +5161,3719 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{793A3F1F-EDE2-4286-8BE0-AB079BDFCB3C}">
+  <dimension ref="B1:W120"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="8.88671875" style="31"/>
+    <col min="15" max="15" width="10.77734375" style="55" customWidth="1"/>
+    <col min="16" max="16" width="28.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:17" s="50" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="50" t="s">
+        <v>831</v>
+      </c>
+      <c r="I1" s="52"/>
+      <c r="O1" s="54"/>
+    </row>
+    <row r="2" spans="2:17" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="Q2" s="47" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B3" t="str" cm="1">
+        <f t="array" ref="B3:N9">_xlfn._xlws.FILTER(staff[],LEFT(staff[First Name],1)="H")</f>
+        <v>PR00246</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Husein</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Augar</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G3">
+        <v>67905.8</v>
+      </c>
+      <c r="H3" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I3" s="31">
+        <v>44194</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M3">
+        <v>3.4794520547945207</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="15" x14ac:dyDescent="0.3">
+      <c r="B4" t="str">
+        <v>PR00746</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="G4">
+        <v>114177.23</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="I4" s="31">
+        <v>43908</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="M4">
+        <v>4.2630136986301368</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Full time</v>
+      </c>
+      <c r="Q4" s="45"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B5" t="str">
+        <v>SQ04437</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Hephzibah</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Summerell</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Services</v>
+      </c>
+      <c r="G5">
+        <v>28305.08</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I5" s="31">
+        <v>43754</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="M5">
+        <v>4.6849315068493151</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="B6" t="str">
+        <v>TN00214</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Hemavati</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Muthiah</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Training</v>
+      </c>
+      <c r="G6">
+        <v>37902.35</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I6" s="31">
+        <v>43823</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M6">
+        <v>4.4958904109589044</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Full time</v>
+      </c>
+      <c r="Q6" s="46" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <v>TN04175</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Hinda</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Label</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G7">
+        <v>92704.48</v>
+      </c>
+      <c r="H7" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I7" s="31">
+        <v>43430</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="M7">
+        <v>5.5726027397260278</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="B8" t="str">
+        <v>TN04775</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Hridaynath</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Tendulkar</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Female</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="G8">
+        <v>31089.22</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="I8" s="31">
+        <v>43776</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="M8">
+        <v>4.624657534246575</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Full time</v>
+      </c>
+      <c r="Q8" s="46" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B9" t="str">
+        <v>VT01996</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Hali</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Behnecke</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Male</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="G9">
+        <v>65569.36</v>
+      </c>
+      <c r="H9" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="I9" s="31">
+        <v>43293</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="M9">
+        <v>5.9479452054794519</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="Q10" s="46" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" s="51" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q11"/>
+    </row>
+    <row r="12" spans="2:17" ht="23.4" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>844</v>
+      </c>
+      <c r="L12" s="47" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q12" s="46" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="B13" s="46" t="s">
+        <v>839</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="B15" s="46" t="s">
+        <v>840</v>
+      </c>
+      <c r="L15" s="46" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" ht="15" x14ac:dyDescent="0.35">
+      <c r="B17" s="46" t="s">
+        <v>841</v>
+      </c>
+      <c r="L17" s="46" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" ht="15" x14ac:dyDescent="0.35">
+      <c r="B19" s="46" t="s">
+        <v>842</v>
+      </c>
+      <c r="L19" s="46" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" ht="15" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>843</v>
+      </c>
+      <c r="L21" s="46" t="s">
+        <v>850</v>
+      </c>
+      <c r="O21"/>
+      <c r="P21" s="55"/>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="I24"/>
+      <c r="J24" s="31"/>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B25" s="51"/>
+      <c r="C25" s="51" t="s">
+        <v>832</v>
+      </c>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51" t="s">
+        <v>833</v>
+      </c>
+      <c r="J25" s="53"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="51"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="51"/>
+      <c r="R25" s="51"/>
+      <c r="S25" s="51"/>
+      <c r="T25" s="51"/>
+      <c r="U25" s="51"/>
+      <c r="V25" s="51"/>
+      <c r="W25" s="51"/>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="I26"/>
+      <c r="J26" s="31"/>
+      <c r="O26"/>
+      <c r="P26" s="55"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C27" t="str" cm="1">
+        <f t="array" ref="C27:E48">_xlfn._xlws.FILTER(staff[[Emp ID]:[Last Name]],MONTH(staff[Start Date])=3)</f>
+        <v>PR00746</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Hogan</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Iles</v>
+      </c>
+      <c r="I27"/>
+      <c r="J27" s="31"/>
+      <c r="O27"/>
+      <c r="P27" s="55"/>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C28" t="str">
+        <v>PR00893</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Vasavi</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Veeravasarapu</v>
+      </c>
+      <c r="I28" t="str" cm="1">
+        <f t="array" ref="I28:U89">_xlfn._xlws.FILTER(staff[],(WEEKDAY(staff[Start Date],2)=1)*(staff[Gender]="Female"))</f>
+        <v>PR00007</v>
+      </c>
+      <c r="J28" s="31" t="str">
+        <v>Torrance</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Collier</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N28">
+        <v>96135.75</v>
+      </c>
+      <c r="O28" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P28" s="55">
+        <v>44025</v>
+      </c>
+      <c r="Q28">
+        <v>0.3</v>
+      </c>
+      <c r="R28" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S28" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="T28">
+        <v>3.9424657534246577</v>
+      </c>
+      <c r="U28" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C29" t="str">
+        <v>SQ00022</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Carlin</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Demke</v>
+      </c>
+      <c r="I29" t="str">
+        <v>PR00095</v>
+      </c>
+      <c r="J29" s="31" t="str">
+        <v>Devrat</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Damarsingh</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N29">
+        <v>70649.460000000006</v>
+      </c>
+      <c r="O29" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P29" s="55">
+        <v>43843</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S29" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T29">
+        <v>4.441095890410959</v>
+      </c>
+      <c r="U29" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C30" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Ragunathan</v>
+      </c>
+      <c r="I30" t="str">
+        <v>PR00113</v>
+      </c>
+      <c r="J30" s="31" t="str">
+        <v>Van</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N30">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="O30" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P30" s="55">
+        <v>43360</v>
+      </c>
+      <c r="Q30">
+        <v>1</v>
+      </c>
+      <c r="R30" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S30" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T30">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="U30" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C31" t="str">
+        <v>SQ01519</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Caron</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Kolakovic</v>
+      </c>
+      <c r="I31" t="str">
+        <v>PR00113</v>
+      </c>
+      <c r="J31" s="31" t="str">
+        <v>Van</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N31">
+        <v>85000</v>
+      </c>
+      <c r="O31" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P31" s="55">
+        <v>43360</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="R31" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S31" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T31">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="U31" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="C32" t="str">
+        <v>SQ03112</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Kantimoy</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Pritish</v>
+      </c>
+      <c r="I32" t="str">
+        <v>PR00576</v>
+      </c>
+      <c r="J32" s="31" t="str">
+        <v>Lalitchandra</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Vadali</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="N32">
+        <v>63705.4</v>
+      </c>
+      <c r="O32" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P32" s="55">
+        <v>43682</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="R32" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S32" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T32">
+        <v>4.882191780821918</v>
+      </c>
+      <c r="U32" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C33" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Artis</v>
+      </c>
+      <c r="I33" t="str">
+        <v>PR00916</v>
+      </c>
+      <c r="J33" s="31" t="str">
+        <v>Inger</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Chapelhow</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="N33">
+        <v>84309.95</v>
+      </c>
+      <c r="O33" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P33" s="55">
+        <v>44501</v>
+      </c>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S33" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T33">
+        <v>2.6383561643835618</v>
+      </c>
+      <c r="U33" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C34" t="str">
+        <v>SQ04612</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Spraberry</v>
+      </c>
+      <c r="I34" t="str">
+        <v>PR01383</v>
+      </c>
+      <c r="J34" s="31" t="str">
+        <v>Addi</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Studdeard</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N34">
+        <v>72502.61</v>
+      </c>
+      <c r="O34" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P34" s="55">
+        <v>44235</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S34" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="T34">
+        <v>3.3671232876712329</v>
+      </c>
+      <c r="U34" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C35" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Shattesh</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Utpat</v>
+      </c>
+      <c r="I35" t="str">
+        <v>PR02016</v>
+      </c>
+      <c r="J35" s="31" t="str">
+        <v>Iris</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Wagg</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="N35">
+        <v>58861.19</v>
+      </c>
+      <c r="O35" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P35" s="55">
+        <v>43654</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+      <c r="R35" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S35" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T35">
+        <v>4.9589041095890414</v>
+      </c>
+      <c r="U35" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="36" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C36" t="str">
+        <v>TN01256</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Sawini</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Chandan</v>
+      </c>
+      <c r="I36" t="str">
+        <v>PR02113</v>
+      </c>
+      <c r="J36" s="31" t="str">
+        <v>Beverie</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Moffet</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Support</v>
+      </c>
+      <c r="N36">
+        <v>75974.990000000005</v>
+      </c>
+      <c r="O36" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P36" s="55">
+        <v>44172</v>
+      </c>
+      <c r="Q36">
+        <v>1</v>
+      </c>
+      <c r="R36" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S36" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T36">
+        <v>3.5397260273972604</v>
+      </c>
+      <c r="U36" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="37" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C37" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="I37" t="str">
+        <v>PR02275</v>
+      </c>
+      <c r="J37" s="31" t="str">
+        <v>Louise</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Lamming</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N37">
+        <v>41934.71</v>
+      </c>
+      <c r="O37" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P37" s="55">
+        <v>43780</v>
+      </c>
+      <c r="Q37">
+        <v>1</v>
+      </c>
+      <c r="R37" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S37" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T37">
+        <v>4.6136986301369864</v>
+      </c>
+      <c r="U37" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="38" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C38" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="I38" t="str">
+        <v>PR02436</v>
+      </c>
+      <c r="J38" s="31" t="str">
+        <v>Marmaduke</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Worssam</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="N38">
+        <v>78378.2</v>
+      </c>
+      <c r="O38" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P38" s="55">
+        <v>43465</v>
+      </c>
+      <c r="Q38">
+        <v>0.4</v>
+      </c>
+      <c r="R38" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S38" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T38">
+        <v>5.4767123287671229</v>
+      </c>
+      <c r="U38" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="39" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C39" t="str">
+        <v>TN04892</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Luca</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Wolstenholme</v>
+      </c>
+      <c r="I39" t="str">
+        <v>PR02603</v>
+      </c>
+      <c r="J39" s="31" t="str">
+        <v>Dinanath</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Simhambhatla</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="N39">
+        <v>61994.76</v>
+      </c>
+      <c r="O39" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P39" s="55">
+        <v>43794</v>
+      </c>
+      <c r="Q39">
+        <v>0.3</v>
+      </c>
+      <c r="R39" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S39" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T39">
+        <v>4.5753424657534243</v>
+      </c>
+      <c r="U39" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="40" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C40" t="str">
+        <v>VT01762</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Geena</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Raghavanpillai</v>
+      </c>
+      <c r="I40" t="str">
+        <v>PR03158</v>
+      </c>
+      <c r="J40" s="31" t="str">
+        <v>Danica</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Nayshe</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Services</v>
+      </c>
+      <c r="N40">
+        <v>89690.38</v>
+      </c>
+      <c r="O40" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P40" s="55">
+        <v>43206</v>
+      </c>
+      <c r="Q40">
+        <v>1</v>
+      </c>
+      <c r="R40" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S40" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="T40">
+        <v>6.1863013698630134</v>
+      </c>
+      <c r="U40" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="41" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C41" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Linford</v>
+      </c>
+      <c r="I41" t="str">
+        <v>PR04380</v>
+      </c>
+      <c r="J41" s="31" t="str">
+        <v>Van</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N41">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="O41" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P41" s="55">
+        <v>43787</v>
+      </c>
+      <c r="Q41">
+        <v>0.8</v>
+      </c>
+      <c r="R41" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S41" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T41">
+        <v>4.5945205479452058</v>
+      </c>
+      <c r="U41" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="42" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C42" t="str">
+        <v>VT02417</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Evangelina</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Lergan</v>
+      </c>
+      <c r="I42" t="str">
+        <v>PR04446</v>
+      </c>
+      <c r="J42" s="31" t="str">
+        <v>Sameer</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Shashank</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="N42">
+        <v>92336.08</v>
+      </c>
+      <c r="O42" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P42" s="55">
+        <v>44431</v>
+      </c>
+      <c r="Q42">
+        <v>1</v>
+      </c>
+      <c r="R42" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S42" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T42">
+        <v>2.8301369863013699</v>
+      </c>
+      <c r="U42" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="43" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C43" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="I43" t="str">
+        <v>PR04473</v>
+      </c>
+      <c r="J43" s="31" t="str">
+        <v>Wyn</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Treadger</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N43">
+        <v>69192.850000000006</v>
+      </c>
+      <c r="O43" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P43" s="55">
+        <v>44305</v>
+      </c>
+      <c r="Q43">
+        <v>1</v>
+      </c>
+      <c r="R43" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S43" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T43">
+        <v>3.1753424657534248</v>
+      </c>
+      <c r="U43" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="44" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C44" t="str">
+        <v>VT03421</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Alic</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Bagg</v>
+      </c>
+      <c r="I44" t="str">
+        <v>PR04686</v>
+      </c>
+      <c r="J44" s="31" t="str">
+        <v>Oona</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Donan</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N44">
+        <v>98000</v>
+      </c>
+      <c r="O44" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P44" s="55">
+        <v>43710</v>
+      </c>
+      <c r="Q44">
+        <v>0.9</v>
+      </c>
+      <c r="R44" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S44" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T44">
+        <v>4.8054794520547945</v>
+      </c>
+      <c r="U44" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="45" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C45" t="str">
+        <v>VT03993</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Dulce</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Colbeck</v>
+      </c>
+      <c r="I45" t="str">
+        <v>SQ00105</v>
+      </c>
+      <c r="J45" s="31" t="str">
+        <v>Sarayu</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Ragunathan</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N45">
+        <v>86010.54</v>
+      </c>
+      <c r="O45" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P45" s="55">
+        <v>43164</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S45" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T45">
+        <v>6.3013698630136989</v>
+      </c>
+      <c r="U45" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="46" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C46" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="I46" t="str">
+        <v>SQ00841</v>
+      </c>
+      <c r="J46" s="31" t="str">
+        <v>Bhuvan</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Pals</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Services</v>
+      </c>
+      <c r="N46">
+        <v>89690.38</v>
+      </c>
+      <c r="O46" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P46" s="55">
+        <v>43213</v>
+      </c>
+      <c r="Q46">
+        <v>1</v>
+      </c>
+      <c r="R46" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S46" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T46">
+        <v>6.1671232876712327</v>
+      </c>
+      <c r="U46" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="47" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C47" t="str">
+        <v>VT04028</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Michale</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Rolf</v>
+      </c>
+      <c r="I47" t="str">
+        <v>SQ00914</v>
+      </c>
+      <c r="J47" s="31" t="str">
+        <v>Duran</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Appala</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N47">
+        <v>38438.239999999998</v>
+      </c>
+      <c r="O47" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P47" s="55">
+        <v>43962</v>
+      </c>
+      <c r="Q47">
+        <v>1</v>
+      </c>
+      <c r="R47" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S47" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T47">
+        <v>4.1150684931506847</v>
+      </c>
+      <c r="U47" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="48" spans="3:21" x14ac:dyDescent="0.3">
+      <c r="C48" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Biles</v>
+      </c>
+      <c r="I48" t="str">
+        <v>SQ00914</v>
+      </c>
+      <c r="J48" s="31" t="str">
+        <v>Karuna</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Pashupathy</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N48">
+        <v>38438.239999999998</v>
+      </c>
+      <c r="O48" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P48" s="55">
+        <v>43962</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
+      </c>
+      <c r="R48" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S48" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T48">
+        <v>4.1150684931506847</v>
+      </c>
+      <c r="U48" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="49" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I49" t="str">
+        <v>SQ01402</v>
+      </c>
+      <c r="J49" s="31" t="str">
+        <v>Sahaj</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Jonnalagadda</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="N49">
+        <v>44403.77</v>
+      </c>
+      <c r="O49" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P49" s="55">
+        <v>43416</v>
+      </c>
+      <c r="Q49">
+        <v>1</v>
+      </c>
+      <c r="R49" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S49" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T49">
+        <v>5.6109589041095891</v>
+      </c>
+      <c r="U49" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="50" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I50" t="str">
+        <v>SQ01730</v>
+      </c>
+      <c r="J50" s="31" t="str">
+        <v>Austine</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Littlewood</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Services</v>
+      </c>
+      <c r="N50">
+        <v>32269.91</v>
+      </c>
+      <c r="O50" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P50" s="55">
+        <v>43346</v>
+      </c>
+      <c r="Q50">
+        <v>1</v>
+      </c>
+      <c r="R50" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S50" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T50">
+        <v>5.8027397260273972</v>
+      </c>
+      <c r="U50" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="51" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I51" t="str">
+        <v>SQ02174</v>
+      </c>
+      <c r="J51" s="31" t="str">
+        <v>Sidoney</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Yitzhok</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="N51">
+        <v>118442.54</v>
+      </c>
+      <c r="O51" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="P51" s="55">
+        <v>44193</v>
+      </c>
+      <c r="Q51">
+        <v>1</v>
+      </c>
+      <c r="R51" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S51" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="T51">
+        <v>3.4821917808219176</v>
+      </c>
+      <c r="U51" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="52" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I52" t="str">
+        <v>SQ03321</v>
+      </c>
+      <c r="J52" s="31" t="str">
+        <v>Gradey</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Litton</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="N52">
+        <v>68887.839999999997</v>
+      </c>
+      <c r="O52" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P52" s="55">
+        <v>43297</v>
+      </c>
+      <c r="Q52">
+        <v>1</v>
+      </c>
+      <c r="R52" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S52" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T52">
+        <v>5.9369863013698634</v>
+      </c>
+      <c r="U52" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="53" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I53" t="str">
+        <v>SQ03350</v>
+      </c>
+      <c r="J53" s="31" t="str">
+        <v>Felice</v>
+      </c>
+      <c r="K53" t="str">
+        <v>McMurty</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N53">
+        <v>66865.490000000005</v>
+      </c>
+      <c r="O53" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P53" s="55">
+        <v>43514</v>
+      </c>
+      <c r="Q53">
+        <v>1</v>
+      </c>
+      <c r="R53" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S53" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T53">
+        <v>5.3424657534246576</v>
+      </c>
+      <c r="U53" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="54" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I54" t="str">
+        <v>SQ03350</v>
+      </c>
+      <c r="J54" s="31" t="str">
+        <v>Felice</v>
+      </c>
+      <c r="K54" t="str">
+        <v>McMurty</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N54">
+        <v>66865.490000000005</v>
+      </c>
+      <c r="O54" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P54" s="55">
+        <v>43514</v>
+      </c>
+      <c r="Q54">
+        <v>1</v>
+      </c>
+      <c r="R54" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S54" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T54">
+        <v>5.3424657534246576</v>
+      </c>
+      <c r="U54" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="55" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I55" t="str">
+        <v>SQ03491</v>
+      </c>
+      <c r="J55" s="31" t="str">
+        <v>Freda</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Legan</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N55">
+        <v>102129.37</v>
+      </c>
+      <c r="O55" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="P55" s="55">
+        <v>44396</v>
+      </c>
+      <c r="Q55">
+        <v>1</v>
+      </c>
+      <c r="R55" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S55" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T55">
+        <v>2.9260273972602739</v>
+      </c>
+      <c r="U55" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="56" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I56" t="str">
+        <v>SQ03546</v>
+      </c>
+      <c r="J56" s="31" t="str">
+        <v>Amlankusum</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Rajabhushan</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="N56">
+        <v>75733.740000000005</v>
+      </c>
+      <c r="O56" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P56" s="55">
+        <v>44382</v>
+      </c>
+      <c r="Q56">
+        <v>1</v>
+      </c>
+      <c r="R56" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S56" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T56">
+        <v>2.9643835616438357</v>
+      </c>
+      <c r="U56" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="57" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I57" t="str">
+        <v>SQ03625</v>
+      </c>
+      <c r="J57" s="31" t="str">
+        <v>Fidela</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Artis</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N57">
+        <v>78020.39</v>
+      </c>
+      <c r="O57" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P57" s="55">
+        <v>43899</v>
+      </c>
+      <c r="Q57">
+        <v>1</v>
+      </c>
+      <c r="R57" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S57" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T57">
+        <v>4.2876712328767121</v>
+      </c>
+      <c r="U57" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="58" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I58" t="str">
+        <v>SQ03626</v>
+      </c>
+      <c r="J58" s="31" t="str">
+        <v>Krishnakanta</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Vellanki</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N58">
+        <v>95677.9</v>
+      </c>
+      <c r="O58" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P58" s="55">
+        <v>44396</v>
+      </c>
+      <c r="Q58">
+        <v>0.3</v>
+      </c>
+      <c r="R58" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S58" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T58">
+        <v>2.9260273972602739</v>
+      </c>
+      <c r="U58" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="59" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I59" t="str">
+        <v>SQ04613</v>
+      </c>
+      <c r="J59" s="31" t="str">
+        <v>Sarojini</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Naueshwara</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="N59">
+        <v>85264.38</v>
+      </c>
+      <c r="O59" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P59" s="55">
+        <v>43220</v>
+      </c>
+      <c r="Q59">
+        <v>1</v>
+      </c>
+      <c r="R59" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S59" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T59">
+        <v>6.1479452054794521</v>
+      </c>
+      <c r="U59" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="60" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I60" t="str">
+        <v>SQ04960</v>
+      </c>
+      <c r="J60" s="31" t="str">
+        <v>Shubhra</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Potla</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M60" t="str">
+        <v>Support</v>
+      </c>
+      <c r="N60">
+        <v>71924.850000000006</v>
+      </c>
+      <c r="O60" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P60" s="55">
+        <v>43822</v>
+      </c>
+      <c r="Q60">
+        <v>1</v>
+      </c>
+      <c r="R60" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S60" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T60">
+        <v>4.4986301369863018</v>
+      </c>
+      <c r="U60" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="61" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I61" t="str">
+        <v>TN00083</v>
+      </c>
+      <c r="J61" s="31" t="str">
+        <v>Chandana</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Sannidhi</v>
+      </c>
+      <c r="L61" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="N61">
+        <v>61688.77</v>
+      </c>
+      <c r="O61" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P61" s="55">
+        <v>43346</v>
+      </c>
+      <c r="Q61">
+        <v>0.9</v>
+      </c>
+      <c r="R61" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S61" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T61">
+        <v>5.8027397260273972</v>
+      </c>
+      <c r="U61" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="62" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I62" t="str">
+        <v>TN00182</v>
+      </c>
+      <c r="J62" s="31" t="str">
+        <v>Camilla</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Castle</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N62">
+        <v>75475.929999999993</v>
+      </c>
+      <c r="O62" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P62" s="55">
+        <v>43794</v>
+      </c>
+      <c r="Q62">
+        <v>1</v>
+      </c>
+      <c r="R62" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S62" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T62">
+        <v>4.5753424657534243</v>
+      </c>
+      <c r="U62" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="63" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I63" t="str">
+        <v>TN00890</v>
+      </c>
+      <c r="J63" s="31" t="str">
+        <v>Mayur</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Kousika</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M63" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N63">
+        <v>71570.990000000005</v>
+      </c>
+      <c r="O63" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P63" s="55">
+        <v>44249</v>
+      </c>
+      <c r="Q63">
+        <v>0.5</v>
+      </c>
+      <c r="R63" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S63" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T63">
+        <v>3.3287671232876712</v>
+      </c>
+      <c r="U63" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="64" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I64" t="str">
+        <v>TN01281</v>
+      </c>
+      <c r="J64" s="31" t="str">
+        <v>Cletus</v>
+      </c>
+      <c r="K64" t="str">
+        <v>McGarahan</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="N64">
+        <v>114425.19</v>
+      </c>
+      <c r="O64" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="P64" s="55">
+        <v>43857</v>
+      </c>
+      <c r="Q64">
+        <v>1</v>
+      </c>
+      <c r="R64" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S64" t="str">
+        <v>Wellington, New Zealand</v>
+      </c>
+      <c r="T64">
+        <v>4.4027397260273968</v>
+      </c>
+      <c r="U64" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="65" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I65" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="J65" s="31" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N65">
+        <v>68795.48</v>
+      </c>
+      <c r="O65" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P65" s="55">
+        <v>44277</v>
+      </c>
+      <c r="Q65">
+        <v>0.2</v>
+      </c>
+      <c r="R65" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S65" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T65">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="U65" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="66" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I66" t="str">
+        <v>TN01601</v>
+      </c>
+      <c r="J66" s="31" t="str">
+        <v>Melva</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Jickells</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N66">
+        <v>68795.48</v>
+      </c>
+      <c r="O66" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P66" s="55">
+        <v>44277</v>
+      </c>
+      <c r="Q66">
+        <v>0.2</v>
+      </c>
+      <c r="R66" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S66" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T66">
+        <v>3.2520547945205478</v>
+      </c>
+      <c r="U66" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="67" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I67" t="str">
+        <v>TN02749</v>
+      </c>
+      <c r="J67" s="31" t="str">
+        <v>Parasuramudu</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Jamakayala</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N67">
+        <v>57002.02</v>
+      </c>
+      <c r="O67" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P67" s="55">
+        <v>43192</v>
+      </c>
+      <c r="Q67">
+        <v>0.7</v>
+      </c>
+      <c r="R67" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S67" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T67">
+        <v>6.2246575342465755</v>
+      </c>
+      <c r="U67" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="68" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I68" t="str">
+        <v>TN02883</v>
+      </c>
+      <c r="J68" s="31" t="str">
+        <v>John</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Joseph</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N68">
+        <v>84762.76</v>
+      </c>
+      <c r="O68" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P68" s="55">
+        <v>43332</v>
+      </c>
+      <c r="Q68">
+        <v>1</v>
+      </c>
+      <c r="R68" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="S68" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T68">
+        <v>5.8410958904109593</v>
+      </c>
+      <c r="U68" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="69" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I69" t="str">
+        <v>TN03575</v>
+      </c>
+      <c r="J69" s="31" t="str">
+        <v>Janina</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Wolverson</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="N69">
+        <v>99683.67</v>
+      </c>
+      <c r="O69" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P69" s="55">
+        <v>43500</v>
+      </c>
+      <c r="Q69">
+        <v>1</v>
+      </c>
+      <c r="R69" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S69" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T69">
+        <v>5.3808219178082188</v>
+      </c>
+      <c r="U69" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="70" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I70" t="str">
+        <v>TN03575</v>
+      </c>
+      <c r="J70" s="31" t="str">
+        <v>Janina</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Wolverson</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="N70">
+        <v>99683.67</v>
+      </c>
+      <c r="O70" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P70" s="55">
+        <v>43500</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
+      </c>
+      <c r="R70" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S70" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T70">
+        <v>5.3808219178082188</v>
+      </c>
+      <c r="U70" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="71" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I71" t="str">
+        <v>TN04067</v>
+      </c>
+      <c r="J71" s="31" t="str">
+        <v>Lea</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Chaplin</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="N71">
+        <v>73488.679999999993</v>
+      </c>
+      <c r="O71" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P71" s="55">
+        <v>43570</v>
+      </c>
+      <c r="Q71">
+        <v>1</v>
+      </c>
+      <c r="R71" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S71" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T71">
+        <v>5.1890410958904107</v>
+      </c>
+      <c r="U71" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="72" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I72" t="str">
+        <v>TN04175</v>
+      </c>
+      <c r="J72" s="31" t="str">
+        <v>Hinda</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Label</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="N72">
+        <v>92704.48</v>
+      </c>
+      <c r="O72" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P72" s="55">
+        <v>43430</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+      <c r="R72" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S72" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T72">
+        <v>5.5726027397260278</v>
+      </c>
+      <c r="U72" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="73" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I73" t="str">
+        <v>TN04246</v>
+      </c>
+      <c r="J73" s="31" t="str">
+        <v>Shaylyn</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Ransbury</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Support</v>
+      </c>
+      <c r="N73">
+        <v>100371.31</v>
+      </c>
+      <c r="O73" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="P73" s="55">
+        <v>44067</v>
+      </c>
+      <c r="Q73">
+        <v>0.8</v>
+      </c>
+      <c r="R73" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S73" t="str">
+        <v>Auckland, New Zealand</v>
+      </c>
+      <c r="T73">
+        <v>3.8273972602739725</v>
+      </c>
+      <c r="U73" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="74" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I74" t="str">
+        <v>TN04740</v>
+      </c>
+      <c r="J74" s="31" t="str">
+        <v>Tristam</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Cuming</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Support</v>
+      </c>
+      <c r="N74">
+        <v>104038.9</v>
+      </c>
+      <c r="O74" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="P74" s="55">
+        <v>43815</v>
+      </c>
+      <c r="Q74">
+        <v>1</v>
+      </c>
+      <c r="R74" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S74" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T74">
+        <v>4.5178082191780824</v>
+      </c>
+      <c r="U74" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="75" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I75" t="str">
+        <v>VT00578</v>
+      </c>
+      <c r="J75" s="31" t="str">
+        <v>Magnum</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Locksley</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Services</v>
+      </c>
+      <c r="N75">
+        <v>42314.39</v>
+      </c>
+      <c r="O75" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P75" s="55">
+        <v>44487</v>
+      </c>
+      <c r="Q75">
+        <v>1</v>
+      </c>
+      <c r="R75" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S75" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T75">
+        <v>2.6767123287671235</v>
+      </c>
+      <c r="U75" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="76" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I76" t="str">
+        <v>VT00596</v>
+      </c>
+      <c r="J76" s="31" t="str">
+        <v>Letisha</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Carrett</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N76">
+        <v>84598.88</v>
+      </c>
+      <c r="O76" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P76" s="55">
+        <v>44116</v>
+      </c>
+      <c r="Q76">
+        <v>1</v>
+      </c>
+      <c r="R76" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S76" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T76">
+        <v>3.6931506849315068</v>
+      </c>
+      <c r="U76" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="77" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I77" t="str">
+        <v>VT00596</v>
+      </c>
+      <c r="J77" s="31" t="str">
+        <v>Letisha</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Carrett</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="N77">
+        <v>84598.88</v>
+      </c>
+      <c r="O77" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P77" s="55">
+        <v>44116</v>
+      </c>
+      <c r="Q77">
+        <v>1</v>
+      </c>
+      <c r="R77" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S77" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T77">
+        <v>3.6931506849315068</v>
+      </c>
+      <c r="U77" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="78" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I78" t="str">
+        <v>VT00740</v>
+      </c>
+      <c r="J78" s="31" t="str">
+        <v>Chitrasen</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Laul</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="N78">
+        <v>46751.7</v>
+      </c>
+      <c r="O78" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P78" s="55">
+        <v>43843</v>
+      </c>
+      <c r="Q78">
+        <v>1</v>
+      </c>
+      <c r="R78" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S78" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T78">
+        <v>4.441095890410959</v>
+      </c>
+      <c r="U78" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="79" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I79" t="str">
+        <v>VT01249</v>
+      </c>
+      <c r="J79" s="31" t="str">
+        <v>Brendan</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Edgeller</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="N79">
+        <v>31042.51</v>
+      </c>
+      <c r="O79" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P79" s="55">
+        <v>44473</v>
+      </c>
+      <c r="Q79">
+        <v>0.3</v>
+      </c>
+      <c r="R79" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S79" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T79">
+        <v>2.7150684931506848</v>
+      </c>
+      <c r="U79" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="80" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I80" t="str">
+        <v>VT01610</v>
+      </c>
+      <c r="J80" s="31" t="str">
+        <v>Dhruv</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Manjunath</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="N80">
+        <v>76303.820000000007</v>
+      </c>
+      <c r="O80" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P80" s="55">
+        <v>43458</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+      <c r="R80" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S80" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T80">
+        <v>5.4958904109589044</v>
+      </c>
+      <c r="U80" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="81" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I81" t="str">
+        <v>VT01610</v>
+      </c>
+      <c r="J81" s="31" t="str">
+        <v>Kunja</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Prashanta</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="N81">
+        <v>76303.820000000007</v>
+      </c>
+      <c r="O81" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P81" s="55">
+        <v>43458</v>
+      </c>
+      <c r="Q81">
+        <v>1</v>
+      </c>
+      <c r="R81" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S81" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T81">
+        <v>5.4958904109589044</v>
+      </c>
+      <c r="U81" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="82" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I82" t="str">
+        <v>VT01803</v>
+      </c>
+      <c r="J82" s="31" t="str">
+        <v>Freddy</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Linford</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N82">
+        <v>93128.34</v>
+      </c>
+      <c r="O82" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P82" s="55">
+        <v>43164</v>
+      </c>
+      <c r="Q82">
+        <v>1</v>
+      </c>
+      <c r="R82" t="str">
+        <v>Fixed Term</v>
+      </c>
+      <c r="S82" t="str">
+        <v>Seattle, USA</v>
+      </c>
+      <c r="T82">
+        <v>6.3013698630136989</v>
+      </c>
+      <c r="U82" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="83" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I83" t="str">
+        <v>VT02374</v>
+      </c>
+      <c r="J83" s="31" t="str">
+        <v>Delphine</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Jewis</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="N83">
+        <v>71823.56</v>
+      </c>
+      <c r="O83" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P83" s="55">
+        <v>43374</v>
+      </c>
+      <c r="Q83">
+        <v>0.3</v>
+      </c>
+      <c r="R83" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S83" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T83">
+        <v>5.7260273972602738</v>
+      </c>
+      <c r="U83" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="84" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I84" t="str">
+        <v>VT02374</v>
+      </c>
+      <c r="J84" s="31" t="str">
+        <v>Delphine</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Jewis</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Accounting</v>
+      </c>
+      <c r="N84">
+        <v>71823.56</v>
+      </c>
+      <c r="O84" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P84" s="55">
+        <v>43374</v>
+      </c>
+      <c r="Q84">
+        <v>0.3</v>
+      </c>
+      <c r="R84" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S84" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T84">
+        <v>5.7260273972602738</v>
+      </c>
+      <c r="U84" t="str">
+        <v>Part time</v>
+      </c>
+    </row>
+    <row r="85" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I85" t="str">
+        <v>VT02532</v>
+      </c>
+      <c r="J85" s="31" t="str">
+        <v>Adey</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Ryal</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="N85">
+        <v>32496.880000000001</v>
+      </c>
+      <c r="O85" t="str">
+        <v>Under 50k</v>
+      </c>
+      <c r="P85" s="55">
+        <v>43234</v>
+      </c>
+      <c r="Q85">
+        <v>1</v>
+      </c>
+      <c r="R85" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S85" t="str">
+        <v>Remote</v>
+      </c>
+      <c r="T85">
+        <v>6.1095890410958908</v>
+      </c>
+      <c r="U85" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="86" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I86" t="str">
+        <v>VT03701</v>
+      </c>
+      <c r="J86" s="31" t="str">
+        <v>Narois</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Motiwala</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N86">
+        <v>89829.33</v>
+      </c>
+      <c r="O86" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P86" s="55">
+        <v>43794</v>
+      </c>
+      <c r="Q86">
+        <v>1</v>
+      </c>
+      <c r="R86" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S86" t="str">
+        <v>Chennai, India</v>
+      </c>
+      <c r="T86">
+        <v>4.5753424657534243</v>
+      </c>
+      <c r="U86" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="87" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I87" t="str">
+        <v>VT03988</v>
+      </c>
+      <c r="J87" s="31" t="str">
+        <v>Venkat</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Kodi</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Support</v>
+      </c>
+      <c r="N87">
+        <v>58935.92</v>
+      </c>
+      <c r="O87" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P87" s="55">
+        <v>43717</v>
+      </c>
+      <c r="Q87">
+        <v>1</v>
+      </c>
+      <c r="R87" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S87" t="str">
+        <v>Hyderabad, India</v>
+      </c>
+      <c r="T87">
+        <v>4.7863013698630139</v>
+      </c>
+      <c r="U87" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="88" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I88" t="str">
+        <v>VT04415</v>
+      </c>
+      <c r="J88" s="31" t="str">
+        <v>Malory</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Biles</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Training</v>
+      </c>
+      <c r="N88">
+        <v>58744.17</v>
+      </c>
+      <c r="O88" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="P88" s="55">
+        <v>43171</v>
+      </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
+      <c r="R88" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S88" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T88">
+        <v>6.2821917808219174</v>
+      </c>
+      <c r="U88" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="89" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I89" t="str">
+        <v>VT04552</v>
+      </c>
+      <c r="J89" s="31" t="str">
+        <v>Theresita</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Chasmer</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Female</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="N89">
+        <v>106665.67</v>
+      </c>
+      <c r="O89" t="str">
+        <v>Above 100k</v>
+      </c>
+      <c r="P89" s="55">
+        <v>43311</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
+      </c>
+      <c r="R89" t="str">
+        <v>Temporary</v>
+      </c>
+      <c r="S89" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="T89">
+        <v>5.8986301369863012</v>
+      </c>
+      <c r="U89" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="90" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I90"/>
+      <c r="J90" s="31"/>
+      <c r="O90"/>
+      <c r="P90" s="55"/>
+    </row>
+    <row r="91" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I91"/>
+      <c r="J91" s="31"/>
+      <c r="O91"/>
+      <c r="P91" s="55"/>
+    </row>
+    <row r="92" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I92"/>
+      <c r="J92" s="31"/>
+      <c r="O92"/>
+      <c r="P92" s="55"/>
+    </row>
+    <row r="93" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I93"/>
+      <c r="J93" s="31"/>
+      <c r="O93"/>
+      <c r="P93" s="55"/>
+    </row>
+    <row r="94" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I94"/>
+      <c r="J94" s="31"/>
+      <c r="O94"/>
+      <c r="P94" s="55"/>
+    </row>
+    <row r="95" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I95"/>
+      <c r="J95" s="31"/>
+      <c r="O95"/>
+      <c r="P95" s="55"/>
+    </row>
+    <row r="96" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I96"/>
+      <c r="J96" s="31"/>
+      <c r="O96"/>
+      <c r="P96" s="55"/>
+    </row>
+    <row r="97" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I97"/>
+      <c r="J97" s="31"/>
+      <c r="O97"/>
+      <c r="P97" s="55"/>
+    </row>
+    <row r="98" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I98"/>
+      <c r="J98" s="31"/>
+      <c r="O98"/>
+      <c r="P98" s="55"/>
+    </row>
+    <row r="99" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I99"/>
+      <c r="J99" s="31"/>
+      <c r="O99"/>
+      <c r="P99" s="55"/>
+    </row>
+    <row r="100" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I100"/>
+      <c r="J100" s="31"/>
+      <c r="O100"/>
+      <c r="P100" s="55"/>
+    </row>
+    <row r="101" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I101"/>
+      <c r="J101" s="31"/>
+      <c r="O101"/>
+      <c r="P101" s="55"/>
+    </row>
+    <row r="102" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I102"/>
+      <c r="J102" s="31"/>
+      <c r="O102"/>
+      <c r="P102" s="55"/>
+    </row>
+    <row r="103" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I103"/>
+      <c r="J103" s="31"/>
+      <c r="O103"/>
+      <c r="P103" s="55"/>
+    </row>
+    <row r="104" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I104"/>
+      <c r="J104" s="31"/>
+      <c r="O104"/>
+      <c r="P104" s="55"/>
+    </row>
+    <row r="105" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I105"/>
+      <c r="J105" s="31"/>
+      <c r="O105"/>
+      <c r="P105" s="55"/>
+    </row>
+    <row r="106" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I106"/>
+      <c r="J106" s="31"/>
+      <c r="O106"/>
+      <c r="P106" s="55"/>
+    </row>
+    <row r="107" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I107"/>
+      <c r="J107" s="31"/>
+      <c r="O107"/>
+      <c r="P107" s="55"/>
+    </row>
+    <row r="108" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I108"/>
+      <c r="J108" s="31"/>
+      <c r="O108"/>
+      <c r="P108" s="55"/>
+    </row>
+    <row r="109" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I109"/>
+      <c r="J109" s="31"/>
+      <c r="O109"/>
+      <c r="P109" s="55"/>
+    </row>
+    <row r="110" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I110"/>
+      <c r="J110" s="31"/>
+      <c r="O110"/>
+      <c r="P110" s="55"/>
+    </row>
+    <row r="111" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I111"/>
+      <c r="J111" s="31"/>
+      <c r="O111"/>
+      <c r="P111" s="55"/>
+    </row>
+    <row r="112" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I112"/>
+      <c r="J112" s="31"/>
+      <c r="O112"/>
+      <c r="P112" s="55"/>
+    </row>
+    <row r="113" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I113"/>
+      <c r="J113" s="31"/>
+      <c r="O113"/>
+      <c r="P113" s="55"/>
+    </row>
+    <row r="114" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I114"/>
+      <c r="J114" s="31"/>
+      <c r="O114"/>
+      <c r="P114" s="55"/>
+    </row>
+    <row r="115" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I115"/>
+      <c r="J115" s="31"/>
+      <c r="O115"/>
+      <c r="P115" s="55"/>
+    </row>
+    <row r="116" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I116"/>
+      <c r="J116" s="31"/>
+      <c r="O116"/>
+      <c r="P116" s="55"/>
+    </row>
+    <row r="117" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I117"/>
+      <c r="J117" s="31"/>
+      <c r="O117"/>
+      <c r="P117" s="55"/>
+    </row>
+    <row r="118" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I118"/>
+      <c r="J118" s="31"/>
+      <c r="O118"/>
+      <c r="P118" s="55"/>
+    </row>
+    <row r="119" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I119"/>
+      <c r="J119" s="31"/>
+      <c r="O119"/>
+      <c r="P119" s="55"/>
+    </row>
+    <row r="120" spans="9:16" x14ac:dyDescent="0.3">
+      <c r="I120"/>
+      <c r="J120" s="31"/>
+      <c r="O120"/>
+      <c r="P120" s="55"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C279491-31E5-4EC9-B32C-C00A45CF80AE}">
+  <dimension ref="A2:J16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="61" customWidth="1"/>
+    <col min="5" max="6" width="10.77734375" style="61" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="27" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" s="57" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="57" t="s">
+        <v>851</v>
+      </c>
+      <c r="C2" s="57">
+        <f>COUNTA(staff[Emp ID])</f>
+        <v>260</v>
+      </c>
+      <c r="D2" s="60">
+        <f>AVERAGE(staff[Salary])</f>
+        <v>73877.880076923073</v>
+      </c>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="59">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+      <c r="H2" s="57">
+        <f>MEDIAN(staff[Salary])</f>
+        <v>73360.38</v>
+      </c>
+      <c r="I2" s="64">
+        <f>COUNTIF(staff[Gender],"Female")/COUNTA(staff[Emp ID])</f>
+        <v>0.48076923076923078</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="57" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>852</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>853</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>855</v>
+      </c>
+      <c r="F4" s="63"/>
+      <c r="G4" s="59" t="s">
+        <v>854</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>856</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="J4" s="58"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" t="str" cm="1">
+        <f t="array" ref="B5:B16">_xlfn._xlws.SORT(_xlfn.UNIQUE(staff[Department]))</f>
+        <v>Accounting</v>
+      </c>
+      <c r="C5" cm="1">
+        <f t="array" ref="C5:C16">COUNTIFS(staff[Department],_xlfn.ANCHORARRAY(B5))</f>
+        <v>26</v>
+      </c>
+      <c r="D5" s="61" cm="1">
+        <f t="array" ref="D5:D16">AVERAGEIFS(staff[Salary],staff[Department],_xlfn.ANCHORARRAY(B5))</f>
+        <v>69806.945769230777</v>
+      </c>
+      <c r="E5" s="61" cm="1">
+        <f t="array" ref="E5:E16">_xlfn.ANCHORARRAY(D5)-D2</f>
+        <v>-4070.934307692296</v>
+      </c>
+      <c r="F5" s="62" cm="1">
+        <f t="array" ref="F5:F16">_xlfn.ANCHORARRAY(D5)-D2</f>
+        <v>-4070.934307692296</v>
+      </c>
+      <c r="G5" s="27" cm="1">
+        <f t="array" ref="G5:G16">_xlfn.MAXIFS(staff[Salary],staff[Department],_xlfn.ANCHORARRAY(B5))</f>
+        <v>119022.49</v>
+      </c>
+      <c r="H5" cm="1">
+        <f t="array" ref="H5">MEDIAN(_xlfn._xlws.FILTER(staff[Salary],staff[Department]=B5))</f>
+        <v>69025.614999999991</v>
+      </c>
+      <c r="I5" s="65">
+        <f>COUNTIFS(staff[Department],B5,staff[Gender],"Female")/COUNTIF(staff[Department],B5)</f>
+        <v>0.34615384615384615</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6" s="61">
+        <v>79947.354230769226</v>
+      </c>
+      <c r="E6" s="61">
+        <v>6069.4741538461531</v>
+      </c>
+      <c r="F6" s="62">
+        <v>6069.4741538461531</v>
+      </c>
+      <c r="G6" s="27">
+        <v>110042.37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" t="str">
+        <v>Engineering</v>
+      </c>
+      <c r="C7">
+        <v>26</v>
+      </c>
+      <c r="D7" s="61">
+        <v>81976.441923076913</v>
+      </c>
+      <c r="E7" s="61">
+        <v>8098.5618461538397</v>
+      </c>
+      <c r="F7" s="62">
+        <v>8098.5618461538397</v>
+      </c>
+      <c r="G7" s="27">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" t="str">
+        <v>Human Resources</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8" s="61">
+        <v>73109.377727272746</v>
+      </c>
+      <c r="E8" s="61">
+        <v>-768.50234965032723</v>
+      </c>
+      <c r="F8" s="62">
+        <v>-768.50234965032723</v>
+      </c>
+      <c r="G8" s="27">
+        <v>103494.94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" t="str">
+        <v>Legal</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9" s="61">
+        <v>67242.51761904762</v>
+      </c>
+      <c r="E9" s="61">
+        <v>-6635.3624578754534</v>
+      </c>
+      <c r="F9" s="62">
+        <v>-6635.3624578754534</v>
+      </c>
+      <c r="G9" s="27">
+        <v>113747.56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
+      </c>
+      <c r="D10" s="61">
+        <v>64441.299999999996</v>
+      </c>
+      <c r="E10" s="61">
+        <v>-9436.5800769230773</v>
+      </c>
+      <c r="F10" s="62">
+        <v>-9436.5800769230773</v>
+      </c>
+      <c r="G10" s="27">
+        <v>104903.79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" t="str">
+        <v>Product Management</v>
+      </c>
+      <c r="C11">
+        <v>29</v>
+      </c>
+      <c r="D11" s="61">
+        <v>75179.064482758593</v>
+      </c>
+      <c r="E11" s="61">
+        <v>1301.18440583552</v>
+      </c>
+      <c r="F11" s="62">
+        <v>1301.18440583552</v>
+      </c>
+      <c r="G11" s="27">
+        <v>115191.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" t="str">
+        <v>Research and Development</v>
+      </c>
+      <c r="C12">
+        <v>18</v>
+      </c>
+      <c r="D12" s="61">
+        <v>66910.765555555554</v>
+      </c>
+      <c r="E12" s="61">
+        <v>-6967.114521367519</v>
+      </c>
+      <c r="F12" s="62">
+        <v>-6967.114521367519</v>
+      </c>
+      <c r="G12" s="27">
+        <v>99683.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" t="str">
+        <v>Sales</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+      <c r="D13" s="61">
+        <v>71897.095555555556</v>
+      </c>
+      <c r="E13" s="61">
+        <v>-1980.7845213675173</v>
+      </c>
+      <c r="F13" s="62">
+        <v>-1980.7845213675173</v>
+      </c>
+      <c r="G13" s="27">
+        <v>102129.37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" t="str">
+        <v>Services</v>
+      </c>
+      <c r="C14">
+        <v>21</v>
+      </c>
+      <c r="D14" s="61">
+        <v>74673.974761904756</v>
+      </c>
+      <c r="E14" s="61">
+        <v>796.0946849816828</v>
+      </c>
+      <c r="F14" s="62">
+        <v>796.0946849816828</v>
+      </c>
+      <c r="G14" s="27">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B15" t="str">
+        <v>Support</v>
+      </c>
+      <c r="C15">
+        <v>17</v>
+      </c>
+      <c r="D15" s="61">
+        <v>66432.455882352937</v>
+      </c>
+      <c r="E15" s="61">
+        <v>-7445.424194570136</v>
+      </c>
+      <c r="F15" s="62">
+        <v>-7445.424194570136</v>
+      </c>
+      <c r="G15" s="27">
+        <v>104802.63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" t="str">
+        <v>Training</v>
+      </c>
+      <c r="C16">
+        <v>24</v>
+      </c>
+      <c r="D16" s="61">
+        <v>83883.965000000011</v>
+      </c>
+      <c r="E16" s="61">
+        <v>10006.084923076938</v>
+      </c>
+      <c r="F16" s="62">
+        <v>10006.084923076938</v>
+      </c>
+      <c r="G16" s="27">
+        <v>116767.63</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E4:F4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E16">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="0">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E01B6583-A28B-4E9A-9206-EB9546ABAB79}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E01B6583-A28B-4E9A-9206-EB9546ABAB79}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E5:E16</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE182796-6443-4558-9B87-909B73329DFC}">
   <dimension ref="A1:O267"/>
@@ -4707,7 +8942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>627</v>
       </c>
@@ -4748,7 +8983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>309</v>
       </c>
@@ -4789,7 +9024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>608</v>
       </c>
@@ -4830,7 +9065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>608</v>
       </c>
@@ -4847,7 +9082,7 @@
         <v>25</v>
       </c>
       <c r="H11" s="5">
-        <v>80695.740000000005</v>
+        <v>85000</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -4912,7 +9147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>645</v>
       </c>
@@ -4953,7 +9188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>59</v>
       </c>
@@ -4994,7 +9229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>225</v>
       </c>
@@ -5076,7 +9311,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>596</v>
       </c>
@@ -5117,7 +9352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>98</v>
       </c>
@@ -5158,7 +9393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>94</v>
       </c>
@@ -5199,7 +9434,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>291</v>
       </c>
@@ -5240,7 +9475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>590</v>
       </c>
@@ -5322,7 +9557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>294</v>
       </c>
@@ -5363,7 +9598,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>548</v>
       </c>
@@ -5404,7 +9639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>698</v>
       </c>
@@ -5445,7 +9680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>246</v>
       </c>
@@ -5486,7 +9721,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
         <v>609</v>
       </c>
@@ -5527,7 +9762,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
         <v>666</v>
       </c>
@@ -5568,7 +9803,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
         <v>141</v>
       </c>
@@ -5609,7 +9844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
         <v>672</v>
       </c>
@@ -5650,7 +9885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
         <v>389</v>
       </c>
@@ -5691,7 +9926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
         <v>389</v>
       </c>
@@ -5773,7 +10008,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
         <v>533</v>
       </c>
@@ -5814,7 +10049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
         <v>342</v>
       </c>
@@ -5855,7 +10090,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
         <v>392</v>
       </c>
@@ -5937,7 +10172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
         <v>575</v>
       </c>
@@ -6019,7 +10254,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
         <v>445</v>
       </c>
@@ -6060,7 +10295,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
         <v>707</v>
       </c>
@@ -6101,7 +10336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
         <v>115</v>
       </c>
@@ -6142,7 +10377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
         <v>216</v>
       </c>
@@ -6183,7 +10418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
         <v>560</v>
       </c>
@@ -6224,7 +10459,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>273</v>
       </c>
@@ -6265,7 +10500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
         <v>642</v>
       </c>
@@ -6306,7 +10541,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
         <v>118</v>
       </c>
@@ -6347,7 +10582,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>469</v>
       </c>
@@ -6388,7 +10623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
         <v>102</v>
       </c>
@@ -6429,7 +10664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>721</v>
       </c>
@@ -6470,7 +10705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>321</v>
       </c>
@@ -6511,7 +10746,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
         <v>321</v>
       </c>
@@ -6552,7 +10787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
         <v>198</v>
       </c>
@@ -6634,7 +10869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
         <v>258</v>
       </c>
@@ -6675,7 +10910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
         <v>728</v>
       </c>
@@ -6716,7 +10951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
         <v>282</v>
       </c>
@@ -6757,7 +10992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
         <v>413</v>
       </c>
@@ -6798,7 +11033,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
         <v>69</v>
       </c>
@@ -6880,7 +11115,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
         <v>21</v>
       </c>
@@ -6921,7 +11156,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
         <v>624</v>
       </c>
@@ -7003,7 +11238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
         <v>578</v>
       </c>
@@ -7044,7 +11279,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
         <v>510</v>
       </c>
@@ -7126,7 +11361,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
         <v>605</v>
       </c>
@@ -7167,7 +11402,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
         <v>657</v>
       </c>
@@ -7208,7 +11443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
         <v>186</v>
       </c>
@@ -7249,7 +11484,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
         <v>318</v>
       </c>
@@ -7331,7 +11566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C72" t="s">
         <v>55</v>
       </c>
@@ -7372,7 +11607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C73" t="s">
         <v>78</v>
       </c>
@@ -7413,7 +11648,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C74" t="s">
         <v>365</v>
       </c>
@@ -7454,7 +11689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
         <v>210</v>
       </c>
@@ -7495,7 +11730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
         <v>210</v>
       </c>
@@ -7536,7 +11771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C77" t="s">
         <v>407</v>
       </c>
@@ -7577,7 +11812,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
         <v>419</v>
       </c>
@@ -7618,7 +11853,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
         <v>162</v>
       </c>
@@ -7659,7 +11894,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
         <v>416</v>
       </c>
@@ -7700,7 +11935,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
         <v>128</v>
       </c>
@@ -7741,7 +11976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
         <v>183</v>
       </c>
@@ -7782,7 +12017,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
         <v>351</v>
       </c>
@@ -7864,7 +12099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C85" t="s">
         <v>192</v>
       </c>
@@ -7905,7 +12140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
         <v>348</v>
       </c>
@@ -7946,7 +12181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C87" t="s">
         <v>566</v>
       </c>
@@ -7987,7 +12222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C88" t="s">
         <v>431</v>
       </c>
@@ -8028,7 +12263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
         <v>51</v>
       </c>
@@ -8069,7 +12304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C90" t="s">
         <v>410</v>
       </c>
@@ -8110,7 +12345,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
         <v>410</v>
       </c>
@@ -8274,7 +12509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
         <v>333</v>
       </c>
@@ -8315,7 +12550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C96" t="s">
         <v>204</v>
       </c>
@@ -8356,7 +12591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C97" t="s">
         <v>648</v>
       </c>
@@ -8397,7 +12632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C98" t="s">
         <v>513</v>
       </c>
@@ -8438,7 +12673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C99" t="s">
         <v>633</v>
       </c>
@@ -8479,7 +12714,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C100" t="s">
         <v>213</v>
       </c>
@@ -8520,7 +12755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C101" t="s">
         <v>132</v>
       </c>
@@ -8561,7 +12796,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C102" t="s">
         <v>132</v>
       </c>
@@ -8602,7 +12837,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C103" t="s">
         <v>685</v>
       </c>
@@ -8643,7 +12878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C104" t="s">
         <v>688</v>
       </c>
@@ -8725,7 +12960,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C106" t="s">
         <v>451</v>
       </c>
@@ -8766,7 +13001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C107" t="s">
         <v>487</v>
       </c>
@@ -8848,7 +13083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C109" t="s">
         <v>234</v>
       </c>
@@ -8889,7 +13124,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C110" t="s">
         <v>234</v>
       </c>
@@ -8930,7 +13165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C111" t="s">
         <v>669</v>
       </c>
@@ -9012,7 +13247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C113" t="s">
         <v>360</v>
       </c>
@@ -9053,7 +13288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C114" t="s">
         <v>240</v>
       </c>
@@ -9094,7 +13329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C115" t="s">
         <v>240</v>
       </c>
@@ -9258,7 +13493,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C119" t="s">
         <v>312</v>
       </c>
@@ -9299,7 +13534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C120" t="s">
         <v>735</v>
       </c>
@@ -9340,7 +13575,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C121" t="s">
         <v>395</v>
       </c>
@@ -9422,7 +13657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C123" t="s">
         <v>593</v>
       </c>
@@ -9463,7 +13698,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C124" t="s">
         <v>324</v>
       </c>
@@ -9504,7 +13739,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C125" t="s">
         <v>88</v>
       </c>
@@ -9627,7 +13862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C128" t="s">
         <v>704</v>
       </c>
@@ -9709,7 +13944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C130" t="s">
         <v>428</v>
       </c>
@@ -9750,7 +13985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C131" t="s">
         <v>484</v>
       </c>
@@ -9791,7 +14026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C132" t="s">
         <v>285</v>
       </c>
@@ -9832,7 +14067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C133" t="s">
         <v>81</v>
       </c>
@@ -9873,7 +14108,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
         <v>81</v>
       </c>
@@ -9914,7 +14149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C135" t="s">
         <v>174</v>
       </c>
@@ -9955,7 +14190,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
         <v>612</v>
       </c>
@@ -9996,7 +14231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C137" t="s">
         <v>639</v>
       </c>
@@ -10037,7 +14272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C138" t="s">
         <v>91</v>
       </c>
@@ -10119,7 +14354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C140" t="s">
         <v>404</v>
       </c>
@@ -10160,7 +14395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C141" t="s">
         <v>345</v>
       </c>
@@ -10201,7 +14436,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C142" t="s">
         <v>327</v>
       </c>
@@ -10242,7 +14477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C143" t="s">
         <v>327</v>
       </c>
@@ -10283,7 +14518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C144" t="s">
         <v>109</v>
       </c>
@@ -10324,7 +14559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C145" t="s">
         <v>371</v>
       </c>
@@ -10365,7 +14600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C146" t="s">
         <v>357</v>
       </c>
@@ -10406,7 +14641,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C147" t="s">
         <v>466</v>
       </c>
@@ -10447,7 +14682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C148" t="s">
         <v>466</v>
       </c>
@@ -10529,7 +14764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="150" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C150" t="s">
         <v>401</v>
       </c>
@@ -10570,7 +14805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="151" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C151" t="s">
         <v>715</v>
       </c>
@@ -10611,7 +14846,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="152" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C152" t="s">
         <v>621</v>
       </c>
@@ -10652,7 +14887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C153" t="s">
         <v>563</v>
       </c>
@@ -10693,7 +14928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C154" t="s">
         <v>563</v>
       </c>
@@ -10734,7 +14969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
         <v>386</v>
       </c>
@@ -10775,7 +15010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C156" t="s">
         <v>581</v>
       </c>
@@ -10816,7 +15051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
         <v>168</v>
       </c>
@@ -10857,7 +15092,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C158" t="s">
         <v>168</v>
       </c>
@@ -10898,7 +15133,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
         <v>422</v>
       </c>
@@ -10939,7 +15174,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C160" t="s">
         <v>697</v>
       </c>
@@ -10980,7 +15215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C161" t="s">
         <v>660</v>
       </c>
@@ -11021,7 +15256,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C162" t="s">
         <v>718</v>
       </c>
@@ -11062,7 +15297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
         <v>691</v>
       </c>
@@ -11103,7 +15338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C164" t="s">
         <v>252</v>
       </c>
@@ -11144,7 +15379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C165" t="s">
         <v>156</v>
       </c>
@@ -11185,7 +15420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C166" t="s">
         <v>156</v>
       </c>
@@ -11226,7 +15461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
         <v>492</v>
       </c>
@@ -11267,7 +15502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C168" t="s">
         <v>492</v>
       </c>
@@ -11308,7 +15543,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="169" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
         <v>495</v>
       </c>
@@ -11349,7 +15584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C170" t="s">
         <v>38</v>
       </c>
@@ -11390,7 +15625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C171" t="s">
         <v>439</v>
       </c>
@@ -11431,7 +15666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C172" t="s">
         <v>231</v>
       </c>
@@ -11472,7 +15707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C173" t="s">
         <v>722</v>
       </c>
@@ -11513,7 +15748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C174" t="s">
         <v>207</v>
       </c>
@@ -11554,7 +15789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C175" t="s">
         <v>207</v>
       </c>
@@ -11595,7 +15830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C176" t="s">
         <v>377</v>
       </c>
@@ -11636,7 +15871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C177" t="s">
         <v>554</v>
       </c>
@@ -11677,7 +15912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C178" t="s">
         <v>180</v>
       </c>
@@ -11718,7 +15953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C179" t="s">
         <v>180</v>
       </c>
@@ -11759,7 +15994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C180" t="s">
         <v>195</v>
       </c>
@@ -11800,7 +16035,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C181" t="s">
         <v>219</v>
       </c>
@@ -11841,7 +16076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C182" t="s">
         <v>569</v>
       </c>
@@ -11882,7 +16117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C183" t="s">
         <v>106</v>
       </c>
@@ -11923,7 +16158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C184" t="s">
         <v>303</v>
       </c>
@@ -11964,7 +16199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C185" t="s">
         <v>303</v>
       </c>
@@ -12087,7 +16322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C188" t="s">
         <v>539</v>
       </c>
@@ -12128,7 +16363,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="189" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C189" t="s">
         <v>383</v>
       </c>
@@ -12169,7 +16404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="190" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C190" t="s">
         <v>576</v>
       </c>
@@ -12210,7 +16445,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="191" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C191" t="s">
         <v>542</v>
       </c>
@@ -12292,7 +16527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C193" t="s">
         <v>694</v>
       </c>
@@ -12333,7 +16568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C194" t="s">
         <v>237</v>
       </c>
@@ -12374,7 +16609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="195" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C195" t="s">
         <v>237</v>
       </c>
@@ -12415,7 +16650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="196" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C196" t="s">
         <v>475</v>
       </c>
@@ -12497,7 +16732,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="198" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C198" t="s">
         <v>732</v>
       </c>
@@ -12538,7 +16773,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="199" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C199" t="s">
         <v>587</v>
       </c>
@@ -12579,7 +16814,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="200" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C200" t="s">
         <v>636</v>
       </c>
@@ -12620,7 +16855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C201" t="s">
         <v>463</v>
       </c>
@@ -12661,7 +16896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C202" t="s">
         <v>615</v>
       </c>
@@ -12702,7 +16937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="203" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C203" t="s">
         <v>710</v>
       </c>
@@ -12743,7 +16978,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="204" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C204" t="s">
         <v>62</v>
       </c>
@@ -12784,7 +17019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C205" t="s">
         <v>478</v>
       </c>
@@ -12825,7 +17060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C206" t="s">
         <v>478</v>
       </c>
@@ -12866,7 +17101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C207" t="s">
         <v>545</v>
       </c>
@@ -12907,7 +17142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="208" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C208" t="s">
         <v>663</v>
       </c>
@@ -12948,7 +17183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C209" t="s">
         <v>177</v>
       </c>
@@ -12989,7 +17224,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C210" t="s">
         <v>472</v>
       </c>
@@ -13030,7 +17265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C211" t="s">
         <v>572</v>
       </c>
@@ -13071,7 +17306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C212" t="s">
         <v>222</v>
       </c>
@@ -13112,7 +17347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C213" t="s">
         <v>498</v>
       </c>
@@ -13153,7 +17388,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="214" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C214" t="s">
         <v>288</v>
       </c>
@@ -13194,7 +17429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C215" t="s">
         <v>398</v>
       </c>
@@ -13235,7 +17470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C216" t="s">
         <v>398</v>
       </c>
@@ -13317,7 +17552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="218" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C218" t="s">
         <v>516</v>
       </c>
@@ -13358,7 +17593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C219" t="s">
         <v>165</v>
       </c>
@@ -13440,7 +17675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="221" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C221" t="s">
         <v>33</v>
       </c>
@@ -13563,7 +17798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="224" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C224" t="s">
         <v>677</v>
       </c>
@@ -13604,7 +17839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="225" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C225" t="s">
         <v>249</v>
       </c>
@@ -13645,7 +17880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C226" t="s">
         <v>228</v>
       </c>
@@ -13686,7 +17921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="227" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C227" t="s">
         <v>144</v>
       </c>
@@ -13727,7 +17962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="228" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C228" t="s">
         <v>144</v>
       </c>
@@ -13768,7 +18003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C229" t="s">
         <v>425</v>
       </c>
@@ -13809,7 +18044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C230" t="s">
         <v>315</v>
       </c>
@@ -13850,7 +18085,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C231" t="s">
         <v>315</v>
       </c>
@@ -13891,7 +18126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C232" t="s">
         <v>73</v>
       </c>
@@ -13973,7 +18208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="234" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C234" t="s">
         <v>442</v>
       </c>
@@ -14014,7 +18249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="235" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C235" t="s">
         <v>85</v>
       </c>
@@ -14055,7 +18290,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="236" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C236" t="s">
         <v>270</v>
       </c>
@@ -14137,7 +18372,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="238" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C238" t="s">
         <v>584</v>
       </c>
@@ -14178,7 +18413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="239" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C239" t="s">
         <v>261</v>
       </c>
@@ -14301,7 +18536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C242" t="s">
         <v>354</v>
       </c>
@@ -14342,7 +18577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C243" t="s">
         <v>138</v>
       </c>
@@ -14383,7 +18618,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C244" t="s">
         <v>138</v>
       </c>
@@ -14424,7 +18659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C245" t="s">
         <v>481</v>
       </c>
@@ -14465,7 +18700,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C246" t="s">
         <v>380</v>
       </c>
@@ -14506,7 +18741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="247" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C247" t="s">
         <v>454</v>
       </c>
@@ -14547,7 +18782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C248" t="s">
         <v>701</v>
       </c>
@@ -14588,7 +18823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C249" t="s">
         <v>125</v>
       </c>
@@ -14629,7 +18864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="250" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C250" t="s">
         <v>171</v>
       </c>
@@ -14670,7 +18905,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C251" t="s">
         <v>267</v>
       </c>
@@ -14875,7 +19110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C256" t="s">
         <v>112</v>
       </c>
@@ -14916,7 +19151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="257" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C257" t="s">
         <v>602</v>
       </c>
@@ -15039,7 +19274,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C260" t="s">
         <v>522</v>
       </c>
@@ -15080,7 +19315,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="261" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C261" t="s">
         <v>536</v>
       </c>
@@ -15121,7 +19356,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C262" t="s">
         <v>528</v>
       </c>
@@ -15203,7 +19438,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C264" t="s">
         <v>135</v>
       </c>
@@ -15285,7 +19520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="266" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C266" t="s">
         <v>725</v>
       </c>
@@ -15326,7 +19561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="3:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C267" t="s">
         <v>306</v>
       </c>
@@ -15433,10 +19668,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="27">
-        <v>2074326.9500000002</v>
+        <v>2078631.21</v>
       </c>
       <c r="E4" s="27">
-        <v>79781.805769230778</v>
+        <v>79947.354230769226</v>
       </c>
       <c r="F4">
         <v>18</v>
@@ -18401,4 +22636,589 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D00E1FD1-3C76-44C9-A4B3-4EB89CDD4643}">
+  <dimension ref="B1:D23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" s="40" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="40" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>791</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>792</v>
+      </c>
+      <c r="C5" t="str">
+        <f>VLOOKUP(C3,staff[],2,FALSE)</f>
+        <v>Edd</v>
+      </c>
+      <c r="D5" t="str">
+        <f>IFERROR(VLOOKUP(D3,staff[],2,FALSE),"NOT FOUND")</f>
+        <v>NOT FOUND</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>793</v>
+      </c>
+      <c r="C6" t="str">
+        <f>VLOOKUP(C3,staff[],3,FALSE)</f>
+        <v>MacKnockiter</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C7" t="str">
+        <f>VLOOKUP(C3,staff[],5,FALSE)</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>794</v>
+      </c>
+      <c r="C8">
+        <f>VLOOKUP(C3,staff[],6,FALSE)</f>
+        <v>119022.49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>793</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>797</v>
+      </c>
+      <c r="C19">
+        <f>MATCH(C18,staff[Last Name],0)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>796</v>
+      </c>
+      <c r="C21" t="str" cm="1">
+        <f t="array" ref="C21">INDEX(staff[Emp ID],C19)</f>
+        <v>PR00419</v>
+      </c>
+      <c r="D21" t="str">
+        <f>INDEX(staff[Emp ID],MATCH(C18,staff[Last Name],0))</f>
+        <v>PR00419</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>786</v>
+      </c>
+      <c r="C22" t="str" cm="1">
+        <f t="array" ref="C22">INDEX(staff[Department],C19)</f>
+        <v>Business Development</v>
+      </c>
+      <c r="D22" t="str">
+        <f>INDEX(staff[Department],MATCH(C18,staff[Last Name],0))</f>
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>794</v>
+      </c>
+      <c r="C23" cm="1">
+        <f t="array" ref="C23">INDEX(staff[Salary],C19)</f>
+        <v>68980.52</v>
+      </c>
+      <c r="D23">
+        <f>INDEX(staff[Salary],MATCH(C18,staff[Last Name],0))</f>
+        <v>68980.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46924950-FE23-4C73-8E5D-059AC211E248}">
+  <dimension ref="B4:T29"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>791</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>792</v>
+      </c>
+      <c r="C6" t="str">
+        <f>VLOOKUP(C4,staff[],2,FALSE)</f>
+        <v>Edd</v>
+      </c>
+      <c r="E6" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[First Name],"NOT FOUND")</f>
+        <v>Edd</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>793</v>
+      </c>
+      <c r="C7" t="str">
+        <f>VLOOKUP(C4,staff[],3,FALSE)</f>
+        <v>MacKnockiter</v>
+      </c>
+      <c r="E7" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Last Name],"NOT FOUND")</f>
+        <v>MacKnockiter</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>786</v>
+      </c>
+      <c r="C8" t="str">
+        <f>VLOOKUP(C4,staff[],5,FALSE)</f>
+        <v>Accounting</v>
+      </c>
+      <c r="E8" t="str">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Department],"NOT FOUND")</f>
+        <v>Accounting</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>794</v>
+      </c>
+      <c r="C9">
+        <f>VLOOKUP(C4,staff[],6,FALSE)</f>
+        <v>119022.49</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.XLOOKUP(C4,staff[Emp ID],staff[Salary],"NOT FOUND")</f>
+        <v>119022.49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>793</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="H14" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>797</v>
+      </c>
+      <c r="C15">
+        <f>MATCH(C14,staff[Last Name],0)</f>
+        <v>3</v>
+      </c>
+      <c r="H15" t="str" cm="1">
+        <f t="array" ref="H15:T15">_xlfn.XLOOKUP(C14,staff[Last Name],staff[])</f>
+        <v>PR00113</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Van</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Tuxwell</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Female</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Business Development</v>
+      </c>
+      <c r="M15">
+        <v>80695.740000000005</v>
+      </c>
+      <c r="N15" t="str">
+        <v>50k to 100k</v>
+      </c>
+      <c r="O15">
+        <v>43360</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Permanent</v>
+      </c>
+      <c r="R15" t="str">
+        <v>Columbus, USA</v>
+      </c>
+      <c r="S15">
+        <v>5.7643835616438359</v>
+      </c>
+      <c r="T15" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>796</v>
+      </c>
+      <c r="C17" t="str">
+        <f>INDEX(staff[Emp ID],MATCH(C14,staff[Last Name],0))</f>
+        <v>PR00113</v>
+      </c>
+      <c r="E17" t="str">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Emp ID])</f>
+        <v>PR00113</v>
+      </c>
+      <c r="H17" t="str" cm="1">
+        <f t="array" ref="H17:H29">TRANSPOSE(_xlfn.XLOOKUP(C14,staff[Last Name],staff[]))</f>
+        <v>PR00113</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>786</v>
+      </c>
+      <c r="C18" t="str">
+        <f>INDEX(staff[Department],MATCH(C14,staff[Last Name],0))</f>
+        <v>Business Development</v>
+      </c>
+      <c r="E18" t="str">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Department])</f>
+        <v>Business Development</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Van</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>794</v>
+      </c>
+      <c r="C19">
+        <f>INDEX(staff[Salary],MATCH(C14,staff[Last Name],0))</f>
+        <v>80695.740000000005</v>
+      </c>
+      <c r="E19">
+        <f>_xlfn.XLOOKUP(C14,staff[Last Name],staff[Salary])</f>
+        <v>80695.740000000005</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Tuxwell</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H20" t="str">
+        <v>Female</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H21" t="str">
+        <v>Business Development</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>80695.740000000005</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H23" t="str">
+        <v>50k to 100k</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>43360</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H26" t="str">
+        <v>Permanent</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H27" t="str">
+        <v>Columbus, USA</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>5.7643835616438359</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H29" t="str">
+        <v>Full time</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3849749-5E85-46E3-BA12-42323402D9E1}">
+  <dimension ref="B1:I48"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="40" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" s="40" customFormat="1" ht="31.2" x14ac:dyDescent="0.35">
+      <c r="H2" s="43" t="s">
+        <v>806</v>
+      </c>
+      <c r="I2"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C3">
+        <f>MAX(staff[Salary])</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C4" t="str">
+        <f>_xlfn.XLOOKUP(MAX(staff[Salary]),staff[Salary],staff[First Name])</f>
+        <v>Minerva</v>
+      </c>
+      <c r="H4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5" t="str" cm="1">
+        <f t="array" ref="C5">_xlfn.XLOOKUP(MAX(staff[Salary]),staff[Salary],staff[First Name]&amp;" "&amp;staff[Last Name])</f>
+        <v>Minerva Ricardot</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="H6" s="44" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="15" x14ac:dyDescent="0.3">
+      <c r="H8" s="45" t="str">
+        <f>_xlfn.XLOOKUP(MAX(staff[Salary]),staff[Salary],staff[First Name])</f>
+        <v>Minerva</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>801</v>
+      </c>
+      <c r="C9" t="str" cm="1">
+        <f t="array" ref="C9:C10">_xlfn._xlws.FILTER(staff[First Name],staff[Salary]=MAX(staff[Salary]))</f>
+        <v>Minerva</v>
+      </c>
+      <c r="D9" t="s">
+        <v>805</v>
+      </c>
+      <c r="E9" t="str" cm="1">
+        <f t="array" ref="E9">_xlfn.TEXTJOIN(", ",,_xlfn._xlws.FILTER(staff[First Name],staff[Salary]=MAX(staff[Salary])))</f>
+        <v>Minerva, Mick</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.35">
+      <c r="C10" t="str">
+        <v>Mick</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.35">
+      <c r="H12" s="46" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="H16" s="44" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="H18" s="45" t="str" cm="1">
+        <f t="array" ref="H18">_xlfn.XLOOKUP(MAX(staff[Salary]),staff[Salary],staff[First Name]&amp;" "&amp;staff[Last Name])</f>
+        <v>Minerva Ricardot</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H20" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H22" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="H24" s="44" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="26" spans="8:8" ht="15" x14ac:dyDescent="0.3">
+      <c r="H26" s="45" t="str" cm="1">
+        <f t="array" ref="H26:H27">_xlfn._xlws.FILTER(staff[First Name],staff[Salary]=MAX(staff[Salary]))</f>
+        <v>Minerva</v>
+      </c>
+    </row>
+    <row r="27" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H27" t="str">
+        <v>Mick</v>
+      </c>
+    </row>
+    <row r="28" spans="8:8" ht="15" x14ac:dyDescent="0.35">
+      <c r="H28" s="46" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="30" spans="8:8" ht="15" x14ac:dyDescent="0.35">
+      <c r="H30" s="46" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="32" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H32" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="34" spans="8:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="H34" s="44" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="36" spans="8:9" ht="15" x14ac:dyDescent="0.3">
+      <c r="H36" s="45" t="str" cm="1">
+        <f t="array" ref="H36">_xlfn.TEXTJOIN(", ",TRUE,_xlfn._xlws.FILTER(staff[First Name],staff[Salary]=MAX(staff[Salary])))</f>
+        <v>Minerva, Mick</v>
+      </c>
+    </row>
+    <row r="38" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H38" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="40" spans="8:9" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="H40" s="47" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="42" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H42" s="48" t="s">
+        <v>821</v>
+      </c>
+      <c r="I42" s="48" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="43" spans="8:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H43" s="49" t="s">
+        <v>753</v>
+      </c>
+      <c r="I43" s="49" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="44" spans="8:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H44" s="49" t="s">
+        <v>824</v>
+      </c>
+      <c r="I44" s="49" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="45" spans="8:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H45" s="49" t="s">
+        <v>826</v>
+      </c>
+      <c r="I45" s="49" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="46" spans="8:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H46" s="49" t="s">
+        <v>828</v>
+      </c>
+      <c r="I46" s="49" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="48" spans="8:9" ht="15" x14ac:dyDescent="0.35">
+      <c r="H48" t="s">
+        <v>830</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>